--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="O7" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P8" t="n">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="P7" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="O7" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P9" t="n">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P7" t="n">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="O9" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>4.32</v>
+        <v>4.4</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="O7" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>4.32</v>
+        <v>4.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="O6" t="n">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="P6" t="n">
-        <v>3.62</v>
+        <v>4.32</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="P7" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="O6" t="n">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="P6" t="n">
-        <v>4.32</v>
+        <v>3.62</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="P7" t="n">
-        <v>3.62</v>
+        <v>4.32</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O3" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>4.92</v>
+        <v>4.5</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="P4" t="n">
-        <v>4.5</v>
+        <v>4.92</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="P7" t="n">
-        <v>4.32</v>
+        <v>3.62</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="P3" t="n">
-        <v>4.5</v>
+        <v>4.92</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O4" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>4.92</v>
+        <v>4.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P8" t="n">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O3" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>4.92</v>
+        <v>4.5</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="P4" t="n">
-        <v>4.5</v>
+        <v>4.92</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="P7" t="n">
-        <v>3.62</v>
+        <v>4.32</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="O8" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>4.32</v>
+        <v>4.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="P7" t="n">
-        <v>4.32</v>
+        <v>3.62</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="P9" t="n">
-        <v>3.62</v>
+        <v>4.32</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="P3" t="n">
-        <v>4.5</v>
+        <v>4.92</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O4" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>4.92</v>
+        <v>4.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="P9" t="n">
-        <v>4.32</v>
+        <v>3.62</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="P6" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="O6" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="P7" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P6" t="n">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="O7" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="P9" t="n">
-        <v>4.32</v>
+        <v>3.62</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="O6" t="n">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="P6" t="n">
-        <v>4.32</v>
+        <v>3.62</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="P9" t="n">
-        <v>3.62</v>
+        <v>4.32</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O3" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>4.92</v>
+        <v>4.5</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="P4" t="n">
-        <v>4.5</v>
+        <v>4.92</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="O6" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="P9" t="n">
-        <v>4.32</v>
+        <v>3.62</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P6" t="n">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="O7" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>4.32</v>
+        <v>4.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="P3" t="n">
-        <v>4.5</v>
+        <v>4.92</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O4" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>4.92</v>
+        <v>4.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="O6" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>4.32</v>
+        <v>4.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P7" t="n">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P6" t="n">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="O7" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>4.32</v>
+        <v>4.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O3" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>4.92</v>
+        <v>4.5</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="P4" t="n">
-        <v>4.5</v>
+        <v>4.92</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P7" t="n">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="O9" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="P7" t="n">
-        <v>4.32</v>
+        <v>3.62</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P9" t="n">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="P3" t="n">
-        <v>4.5</v>
+        <v>4.92</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O4" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>4.92</v>
+        <v>4.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="P9" t="n">
-        <v>4.32</v>
+        <v>3.62</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P6" t="n">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P7" t="n">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="O7" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>4.32</v>
+        <v>4.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="P9" t="n">
-        <v>3.62</v>
+        <v>4.32</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O3" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>4.92</v>
+        <v>4.5</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="P4" t="n">
-        <v>4.5</v>
+        <v>4.92</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="O6" t="n">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="P6" t="n">
-        <v>3.62</v>
+        <v>4.32</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="P9" t="n">
-        <v>4.32</v>
+        <v>3.62</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="O2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="R2" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S2" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T2" t="n">
         <v>3.42</v>
       </c>
       <c r="U2" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V2" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W2" t="n">
         <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
         <v>1.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AD2" t="n">
         <v>1.47</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.18</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="P3" t="n">
-        <v>4.5</v>
+        <v>4.92</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O4" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>4.92</v>
+        <v>4.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="O6" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>4.32</v>
+        <v>4.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P6" t="n">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="O8" t="n">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.32</v>
+        <v>3.62</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="O9" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -731,7 +731,7 @@
         <v>3.9</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="Q2" t="n">
         <v>3.6</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="O3" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="P3" t="n">
-        <v>4.92</v>
+        <v>4.85</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -926,7 +926,7 @@
         <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="P4" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="O8" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.68</v>
       </c>
       <c r="P9" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="O10" t="n">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="P10" t="n">
-        <v>3.69</v>
+        <v>3.54</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2315,49 +2315,49 @@
         </is>
       </c>
       <c r="N12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.75</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="P12" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P13" t="n">
-        <v>4.01</v>
+        <v>3.61</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="O14" t="n">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="P14" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O2" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.11</v>
+        <v>1.79</v>
       </c>
       <c r="Q2" t="n">
         <v>3.6</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="P3" t="n">
-        <v>4.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="O4" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="P4" t="n">
-        <v>3.9</v>
+        <v>4.85</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="O7" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.68</v>
       </c>
       <c r="P8" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -731,7 +731,7 @@
         <v>3.5</v>
       </c>
       <c r="P2" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
         <v>3.6</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="O3" t="n">
-        <v>3.42</v>
+        <v>3.18</v>
       </c>
       <c r="P3" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="P4" t="n">
         <v>4.85</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="P7" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="O8" t="n">
-        <v>3.68</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="O12" t="n">
         <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>4.68</v>
+        <v>3.91</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="O3" t="n">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="P3" t="n">
-        <v>3.35</v>
+        <v>4.85</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="O4" t="n">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="P4" t="n">
-        <v>4.85</v>
+        <v>3.35</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="O7" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.79</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>3.68</v>
+        <v>3.08</v>
       </c>
       <c r="P9" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2000,10 +2000,10 @@
         <v>1.95</v>
       </c>
       <c r="O10" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="O14" t="n">
         <v>3.45</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="O12" t="n">
         <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>3.91</v>
+        <v>4.2</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="O3" t="n">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="P3" t="n">
-        <v>4.85</v>
+        <v>3.35</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="O4" t="n">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="P4" t="n">
-        <v>3.35</v>
+        <v>4.85</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="O9" t="n">
-        <v>3.08</v>
+        <v>3.75</v>
       </c>
       <c r="P9" t="n">
-        <v>3.62</v>
+        <v>3.85</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="O3" t="n">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="P3" t="n">
-        <v>3.35</v>
+        <v>4.85</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="O4" t="n">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="P4" t="n">
-        <v>4.85</v>
+        <v>3.35</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="O12" t="n">
         <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>4.2</v>
+        <v>3.91</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -731,7 +731,7 @@
         <v>3.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="Q2" t="n">
         <v>3.6</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O4" t="n">
-        <v>3.18</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>3.75</v>
+        <v>3.08</v>
       </c>
       <c r="P9" t="n">
-        <v>3.85</v>
+        <v>3.62</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2636,10 +2636,10 @@
         <v>3.16</v>
       </c>
       <c r="O14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="O9" t="n">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2477,7 +2477,7 @@
         <v>1.85</v>
       </c>
       <c r="O13" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="P13" t="n">
         <v>3.61</v>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="O3" t="n">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>4.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="P4" t="n">
-        <v>3.9</v>
+        <v>4.85</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,49 +1838,49 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.8</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.07</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="P3" t="n">
-        <v>3.9</v>
+        <v>4.85</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="O4" t="n">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>4.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,49 +1520,49 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.8</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.07</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="O8" t="n">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="P9" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O2" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
         <v>3.6</v>
@@ -767,7 +767,7 @@
         <v>1.55</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
         <v>2.6</v>
@@ -890,7 +890,7 @@
         <v>3.58</v>
       </c>
       <c r="P3" t="n">
-        <v>4.85</v>
+        <v>3.95</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="P4" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="O8" t="n">
         <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>1.58</v>
       </c>
       <c r="O9" t="n">
-        <v>3.08</v>
+        <v>3.31</v>
       </c>
       <c r="P9" t="n">
-        <v>3.62</v>
+        <v>4.1</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="P10" t="n">
-        <v>3.2</v>
+        <v>3.92</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="O12" t="n">
         <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>3.91</v>
+        <v>3.95</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2477,10 +2477,10 @@
         <v>1.85</v>
       </c>
       <c r="O13" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>3.61</v>
+        <v>3.7</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.14</v>
+        <v>2.71</v>
       </c>
       <c r="O14" t="n">
         <v>3.35</v>
       </c>
       <c r="P14" t="n">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="O6" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.93</v>
+        <v>3.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.6</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.47</v>
+        <v>2.07</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>3.31</v>
       </c>
       <c r="P8" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.58</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>3.31</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>4.1</v>
+        <v>2.93</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.88</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>3.92</v>
+        <v>2.18</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>1.88</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="P11" t="n">
-        <v>2.18</v>
+        <v>3.92</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
-        <v>3.4</v>
+        <v>2.93</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>2.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.07</v>
+        <v>1.47</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>3.31</v>
       </c>
       <c r="P7" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="O8" t="n">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.93</v>
+        <v>4.3</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>1.88</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="P10" t="n">
-        <v>2.18</v>
+        <v>3.92</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.88</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>3.92</v>
+        <v>2.18</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="O3" t="n">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="P3" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="O4" t="n">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="O6" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.93</v>
+        <v>3.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.6</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.47</v>
+        <v>2.07</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="O7" t="n">
-        <v>3.31</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="P8" t="n">
-        <v>3.4</v>
+        <v>2.93</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>2.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.07</v>
+        <v>1.47</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="O9" t="n">
         <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.88</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>3.92</v>
+        <v>2.18</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>1.88</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="P11" t="n">
-        <v>2.18</v>
+        <v>3.92</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>3.91</v>
+        <v>4.75</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
-        <v>3.4</v>
+        <v>2.93</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>2.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.07</v>
+        <v>1.47</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="O8" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.93</v>
+        <v>4.3</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="Q2" t="n">
         <v>3.6</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="O3" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="O4" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="P4" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="O6" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>2.93</v>
+        <v>4.33</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1520,49 +1520,49 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
         <v>1.7</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AB7" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.76</v>
+        <v>2.12</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="P8" t="n">
-        <v>4.3</v>
+        <v>2.93</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="O9" t="n">
         <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
         <v>3.92</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7</v>
+        <v>3.61</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2636,10 +2636,10 @@
         <v>2.71</v>
       </c>
       <c r="O14" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="P14" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.79</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>3.68</v>
+        <v>2.75</v>
       </c>
       <c r="P7" t="n">
-        <v>3.71</v>
+        <v>2.93</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.12</v>
+        <v>1.79</v>
       </c>
       <c r="O8" t="n">
-        <v>2.75</v>
+        <v>3.68</v>
       </c>
       <c r="P8" t="n">
-        <v>2.93</v>
+        <v>3.71</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="P6" t="n">
-        <v>4.33</v>
+        <v>3.71</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="O7" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>2.93</v>
+        <v>4.3</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="O8" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>3.71</v>
+        <v>4.33</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.76</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>4.3</v>
+        <v>2.93</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="O6" t="n">
-        <v>3.68</v>
+        <v>3.31</v>
       </c>
       <c r="P6" t="n">
-        <v>3.71</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="P7" t="n">
-        <v>4.3</v>
+        <v>2.93</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="P8" t="n">
-        <v>4.33</v>
+        <v>3.71</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.93</v>
+        <v>4.3</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>4.75</v>
+        <v>4.05</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -731,7 +731,7 @@
         <v>3.6</v>
       </c>
       <c r="P2" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
         <v>3.6</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P3" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="O7" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>2.93</v>
+        <v>4.3</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="O8" t="n">
-        <v>3.68</v>
+        <v>2.75</v>
       </c>
       <c r="P8" t="n">
-        <v>3.71</v>
+        <v>2.93</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="O9" t="n">
         <v>3.6</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="O13" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="P13" t="n">
-        <v>3.61</v>
+        <v>4.24</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.71</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="O5" t="n">
         <v>3.42</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="O7" t="n">
         <v>3.6</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
         <v>2.75</v>
       </c>
       <c r="P8" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="O9" t="n">
         <v>3.6</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>3.92</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,14 +2156,14 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P11" t="n">
         <v>1.95</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3.92</v>
-      </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="O12" t="n">
         <v>3.3</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="O6" t="n">
-        <v>3.31</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="P7" t="n">
-        <v>4.3</v>
+        <v>2.93</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.05</v>
+        <v>1.47</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.35</v>
+        <v>1.73</v>
       </c>
       <c r="O8" t="n">
-        <v>2.75</v>
+        <v>3.31</v>
       </c>
       <c r="P8" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="O9" t="n">
         <v>3.6</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2318,10 +2318,10 @@
         <v>1.76</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="O2" t="n">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q2" t="n">
         <v>3.6</v>
@@ -767,7 +767,7 @@
         <v>1.55</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC2" t="n">
         <v>2.6</v>
@@ -1046,7 +1046,7 @@
         <v>1.91</v>
       </c>
       <c r="O4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
         <v>3.75</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="O7" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.93</v>
+        <v>3.78</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.47</v>
+        <v>2.05</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="O8" t="n">
-        <v>3.31</v>
+        <v>3.9</v>
       </c>
       <c r="P8" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>4.3</v>
+        <v>2.93</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>3.92</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.95</v>
+        <v>3.48</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2318,7 +2318,7 @@
         <v>1.76</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P12" t="n">
         <v>4.2</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="O13" t="n">
-        <v>3.85</v>
+        <v>4.01</v>
       </c>
       <c r="P13" t="n">
-        <v>4.24</v>
+        <v>3.95</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="O2" t="n">
         <v>3.08</v>
       </c>
       <c r="P2" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
         <v>3.6</v>
@@ -767,7 +767,7 @@
         <v>1.55</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
         <v>2.6</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="O3" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="P4" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
-        <v>4.75</v>
+        <v>2.93</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>3.78</v>
+        <v>6.5</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="O8" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>2.93</v>
+        <v>3.78</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="O6" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>2.93</v>
+        <v>4.75</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>6.5</v>
+        <v>3.78</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="P8" t="n">
-        <v>4.75</v>
+        <v>2.93</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P9" t="n">
-        <v>3.78</v>
+        <v>6.5</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O10" t="n">
         <v>3.3</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.2</v>
-      </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>3.48</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>3.48</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -702,13 +702,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -717,11 +717,11 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -786,12 +786,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="AJ2" t="n">
@@ -804,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46183.27083333334</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="P3" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="O4" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="P7" t="n">
-        <v>3.78</v>
+        <v>2.93</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="O8" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>2.93</v>
+        <v>3.78</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>3.48</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O11" t="n">
         <v>3.3</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.2</v>
-      </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>3.48</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="O3" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="P4" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="O7" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.93</v>
+        <v>3.78</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
-        <v>3.78</v>
+        <v>4.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>6.5</v>
+        <v>2.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="O12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -864,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -876,72 +876,72 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O3" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="P3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -950,41 +950,41 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46183.58333333334</v>
@@ -1020,130 +1020,130 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="O4" t="n">
         <v>3.58</v>
       </c>
       <c r="P4" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
+          <t>['29', '90+5']</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46183.58333333334</v>
@@ -1205,61 +1205,61 @@
         <v>2.05</v>
       </c>
       <c r="O5" t="n">
-        <v>3.42</v>
+        <v>3.32</v>
       </c>
       <c r="P5" t="n">
-        <v>3.31</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA5" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>6.5</v>
+        <v>4.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK6" t="n">
         <v>2</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="P7" t="n">
-        <v>3.78</v>
+        <v>2.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.05</v>
+        <v>1.47</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,65 +1679,65 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA8" t="n">
         <v>1.72</v>
       </c>
-      <c r="O8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P8" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R8" t="n">
+      <c r="AB8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG8" t="n">
         <v>2.05</v>
       </c>
-      <c r="S8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK8" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>1.4</v>
       </c>
       <c r="O9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="U9" t="n">
         <v>2.75</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.52</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.33</v>
+        <v>2.82</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AE9" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.39</v>
+        <v>1.16</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.52</v>
+        <v>2.62</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="O10" t="n">
         <v>3.3</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.2</v>
-      </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="P11" t="n">
-        <v>3.48</v>
+        <v>3.74</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="O13" t="n">
-        <v>4.01</v>
+        <v>3.78</v>
       </c>
       <c r="P13" t="n">
         <v>3.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>2.68</v>
       </c>
       <c r="O14" t="n">
         <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -1179,26 +1179,26 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
@@ -1281,28 +1281,28 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46183.66666666666</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="P6" t="n">
-        <v>4.55</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.38</v>
+        <v>1.94</v>
       </c>
       <c r="R6" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="S6" t="n">
         <v>1.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="U6" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.06</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.84</v>
+        <v>1.57</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK6" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="O7" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.93</v>
+        <v>3.78</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.16</v>
+        <v>2.25</v>
       </c>
       <c r="R7" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="T7" t="n">
-        <v>2.21</v>
+        <v>3.12</v>
       </c>
       <c r="U7" t="n">
-        <v>3.52</v>
+        <v>2.47</v>
       </c>
       <c r="V7" t="n">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.33</v>
+        <v>3.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.6</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.5</v>
+        <v>2.74</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.52</v>
+        <v>2.1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
-        <v>3.78</v>
+        <v>4.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="T8" t="n">
-        <v>3.12</v>
+        <v>2.69</v>
       </c>
       <c r="U8" t="n">
-        <v>2.47</v>
+        <v>2.9</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.7</v>
+        <v>3.08</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>1.96</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK8" t="n">
         <v>2</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.4</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>7</v>
+        <v>2.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.94</v>
+        <v>3.16</v>
       </c>
       <c r="R9" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="T9" t="n">
-        <v>2.83</v>
+        <v>2.21</v>
       </c>
       <c r="U9" t="n">
-        <v>2.75</v>
+        <v>3.52</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.82</v>
+        <v>2.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.16</v>
+        <v>1.39</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.62</v>
+        <v>1.52</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-10.xlsx
+++ b/jogos_2026-06-10.xlsx
@@ -852,31 +852,31 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -884,107 +884,107 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="O3" t="n">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="P3" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="R3" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="S3" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="T3" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.58</v>
+        <v>3.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.84</v>
+        <v>2.14</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.14</v>
+        <v>2.52</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
+          <t>['29', '90+5']</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>['83']</t>
-        </is>
-      </c>
       <c r="AJ3" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP3" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9</v>
+        <v>1.81</v>
       </c>
       <c r="AS3" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="AT3" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46183.58333333334</v>
@@ -1011,139 +1011,139 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="O4" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z4" t="n">
         <v>3.58</v>
       </c>
-      <c r="P4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AA4" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.14</v>
+        <v>1.84</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.52</v>
+        <v>3.14</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>['29', '90+5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP4" t="n">
         <v>7</v>
       </c>
-      <c r="AN4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>17</v>
-      </c>
       <c r="AQ4" t="n">
-        <v>1.54</v>
+        <v>1.76</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.81</v>
+        <v>0.9</v>
       </c>
       <c r="AS4" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="AT4" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46183.58333333334</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="O6" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="P6" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.94</v>
+        <v>2.45</v>
       </c>
       <c r="R6" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T6" t="n">
-        <v>2.83</v>
+        <v>2.66</v>
       </c>
       <c r="U6" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.82</v>
+        <v>3.08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.62</v>
+        <v>1.93</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="O8" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="P8" t="n">
-        <v>4.55</v>
+        <v>2.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.38</v>
+        <v>3.36</v>
       </c>
       <c r="R8" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.69</v>
+        <v>2.23</v>
       </c>
       <c r="U8" t="n">
-        <v>2.9</v>
+        <v>3.44</v>
       </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.08</v>
+        <v>2.35</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.96</v>
+        <v>2.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.77</v>
+        <v>1.51</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.42</v>
+        <v>5.14</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
         <v>1.04</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AK8" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>1.42</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75</v>
+        <v>3.88</v>
       </c>
       <c r="P9" t="n">
-        <v>2.93</v>
+        <v>7.16</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.16</v>
+        <v>1.86</v>
       </c>
       <c r="R9" t="n">
-        <v>1.87</v>
+        <v>2.13</v>
       </c>
       <c r="S9" t="n">
-        <v>1.61</v>
+        <v>1.39</v>
       </c>
       <c r="T9" t="n">
-        <v>2.21</v>
+        <v>2.8</v>
       </c>
       <c r="U9" t="n">
-        <v>3.52</v>
+        <v>2.7</v>
       </c>
       <c r="V9" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.33</v>
+        <v>3.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AE9" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.52</v>
+        <v>2.52</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.62</v>
+        <v>3.78</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
         <v>2.73</v>
       </c>
       <c r="U10" t="n">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="V10" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE10" t="n">
         <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK10" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.21</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="O12" t="n">
         <v>3.4</v>
@@ -2324,16 +2324,16 @@
         <v>4.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="R12" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="S12" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T12" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="U12" t="n">
         <v>3.16</v>
@@ -2345,34 +2345,34 @@
         <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="AD12" t="n">
         <v>1.18</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
